--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94419783</v>
+        <v>136643837</v>
       </c>
       <c r="B2" t="n">
-        <v>99026</v>
+        <v>79474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219788</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Odrolstjärnen, Jmt</t>
+          <t>Öster om Odrolstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472824</v>
+        <v>472816</v>
       </c>
       <c r="R2" t="n">
-        <v>7028800</v>
+        <v>7028973</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,71 +762,100 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94419783</t>
+          <t>https://artportalen.se/Sighting/136643837</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94419766</v>
+        <v>136643838</v>
       </c>
       <c r="B3" t="n">
-        <v>99022</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Odrolstjärnen, Jmt</t>
+          <t>Öster om Odrolstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472824</v>
+        <v>472798</v>
       </c>
       <c r="R3" t="n">
-        <v>7028800</v>
+        <v>7029017</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +879,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,24 +893,4042 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136643838</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136643839</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>472808</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7028998</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643839</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136643840</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>472914</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7028875</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643840</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136643841</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>472906</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7028830</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643841</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136643842</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>472915</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7028770</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en stående död gran.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643842</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136643843</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>472998</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7028765</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643843</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136643844</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>473028</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7028801</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643844</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136643845</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>472991</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7028748</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643845</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136643846</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>472938</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7028736</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643846</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136643824</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>472871</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7028958</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre grova hackspår i stambasen av en stående död grov gran.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643824</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136643814</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>472819</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7028971</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, enstaka på en gran nära vägen.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643814</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136643815</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>472857</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7028945</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 st. gamla bohål med ca 40 - 45 mm i diameter och på ca 1,6 meters och 2 meters höjd i en granhögstubbe med tajgagranticka. Även ett till påbörjat bohål finns i granhögstubben. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. Liknande nivå av livsmiljövärde finns i flera delar av det omgivande skogsbeståndet.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643815</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136643816</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>472939</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7028771</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 födosökande tretåig hackspett som efter observerationen flög österut. Denna tretåiga hackspett sågs en mycket kort stund högt upp på en stående död gran och hann tyvärr inte fotas. Likaså gick den ej att könsbestämma den korta stund den syntes till. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett. Liknande nivå av livsmiljövärde finns i flera delar av det omgivande skogsbeståndet.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643816</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136643817</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>473033</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7028734</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran i barrblandskog med stor stamdiameterspridning. Spår av sav/kådaflöde i hackhålen.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643817</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136643818</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>473009</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7028729</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, några meter upp på en gran vid kant mot ungskog.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643818</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136643819</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>472987</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7028746</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, några meter upp på en tall i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643819</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136643820</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>472914</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7028654</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, några meter upp på en tall i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643820</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136643821</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58162</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>472896</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7028684</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643821</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>94419783</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>472824</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7028800</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-06-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-06-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94419783</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>94419766</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>472824</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7028800</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-06-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-06-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/94419766</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136643825</v>
+      </c>
+      <c r="B23" t="n">
+        <v>111317</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>472858</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7028980</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643825</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136643827</v>
+      </c>
+      <c r="B24" t="n">
+        <v>111317</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>472928</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7028852</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643827</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136643828</v>
+      </c>
+      <c r="B25" t="n">
+        <v>111317</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>473062</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7028779</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643828</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136643829</v>
+      </c>
+      <c r="B26" t="n">
+        <v>111317</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>472873</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7028737</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643829</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136643830</v>
+      </c>
+      <c r="B27" t="n">
+        <v>111317</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>472956</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7028651</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>I flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643830</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136643831</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>472820</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7028978</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor och 1 överblommad blomställning inom ca 3 x 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643831</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136643832</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>472805</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7029002</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 6 plantor inom ca 0,5 m2 yta i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643832</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136643833</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>472835</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7028998</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 45 plantor inom ca 1 m2 yta i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643833</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136643834</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>472854</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7028980</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 13 plantor och 1 överblommad blomställning inom ca 0,5 m2 yta i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643834</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136643835</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>472890</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7028866</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor varav med 2 överblommade blomställningar inom ca 2 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643835</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136643823</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99364</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>472836</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7028998</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643823</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136643836</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98393</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Öster om Odrolstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>472857</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7028911</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136643836</t>
         </is>
       </c>
     </row>
@@ -886,6 +4936,37 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111317</v>
+        <v>111324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111317</v>
+        <v>111324</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111317</v>
+        <v>111324</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111317</v>
+        <v>111324</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111317</v>
+        <v>111324</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98393</v>
+        <v>98396</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111324</v>
+        <v>111325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111324</v>
+        <v>111325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111324</v>
+        <v>111325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111324</v>
+        <v>111325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111324</v>
+        <v>111325</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98396</v>
+        <v>98397</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136643837</v>
       </c>
       <c r="B2" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136643838</v>
       </c>
       <c r="B3" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136643839</v>
       </c>
       <c r="B4" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136643840</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136643841</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136643842</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>136643843</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136643844</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136643845</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136643846</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136643824</v>
       </c>
       <c r="B12" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>136643814</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136643815</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>136643816</v>
       </c>
       <c r="B15" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>136643817</v>
       </c>
       <c r="B16" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>136643818</v>
       </c>
       <c r="B17" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>136643819</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>136643820</v>
       </c>
       <c r="B19" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>136643821</v>
       </c>
       <c r="B20" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111325</v>
+        <v>111330</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111325</v>
+        <v>111330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111325</v>
+        <v>111330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111325</v>
+        <v>111330</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111325</v>
+        <v>111330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99368</v>
+        <v>99373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98397</v>
+        <v>98402</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99373</v>
+        <v>99375</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98402</v>
+        <v>98404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136643837</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136643838</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136643839</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136643840</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136643841</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136643842</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>136643843</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136643844</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136643845</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136643846</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99375</v>
+        <v>99381</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98404</v>
+        <v>98410</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136643837</v>
       </c>
       <c r="B2" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136643838</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136643839</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136643840</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136643841</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136643842</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>136643843</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136643844</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136643845</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136643846</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99381</v>
+        <v>99383</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136643837</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136643838</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136643839</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136643840</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136643841</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136643842</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>136643843</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136643844</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136643845</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136643846</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99383</v>
+        <v>99384</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98412</v>
+        <v>98413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99384</v>
+        <v>99390</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98413</v>
+        <v>98419</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136643837</v>
       </c>
       <c r="B2" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136643838</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136643839</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136643840</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136643841</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136643842</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>136643843</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136643844</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136643845</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136643846</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99390</v>
+        <v>99394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98419</v>
+        <v>98423</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98423</v>
+        <v>98425</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136643837</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136643838</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136643839</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136643840</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136643841</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136643842</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>136643843</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136643844</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136643845</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136643846</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98425</v>
+        <v>98427</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136643837</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136643838</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136643839</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136643840</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136643841</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136643842</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>136643843</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136643844</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136643845</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136643846</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136643824</v>
       </c>
       <c r="B12" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>136643814</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136643815</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>136643816</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>136643817</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>136643818</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>136643819</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>136643820</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>136643821</v>
       </c>
       <c r="B20" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99398</v>
+        <v>99411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98427</v>
+        <v>98440</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 33052-2026 artfynd.xlsx
+++ b/artfynd/A 33052-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136643837</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136643838</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136643839</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136643840</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136643841</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136643842</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>136643843</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136643844</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136643845</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136643846</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136643824</v>
       </c>
       <c r="B12" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>136643814</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136643815</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>136643816</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>136643817</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>136643818</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>136643819</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>136643820</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>136643821</v>
       </c>
       <c r="B20" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136643825</v>
       </c>
       <c r="B23" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>136643827</v>
       </c>
       <c r="B24" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136643828</v>
       </c>
       <c r="B25" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136643829</v>
       </c>
       <c r="B26" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>136643830</v>
       </c>
       <c r="B27" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136643831</v>
       </c>
       <c r="B28" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>136643832</v>
       </c>
       <c r="B29" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>136643833</v>
       </c>
       <c r="B30" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>136643834</v>
       </c>
       <c r="B31" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136643835</v>
       </c>
       <c r="B32" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136643823</v>
       </c>
       <c r="B33" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>136643836</v>
       </c>
       <c r="B34" t="n">
-        <v>98440</v>
+        <v>98442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
